--- a/extract2.xlsx
+++ b/extract2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://smailiitmacin-my.sharepoint.com/personal/mm21b044_smail_iitm_ac_in/Documents/DDP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34E220F2-FBFD-4970-8BB4-97F5E3A450CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="8_{34E220F2-FBFD-4970-8BB4-97F5E3A450CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F300808-0F85-4DEB-AD04-746DEE5E5C89}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{9CD1172C-BCCA-4C90-96AB-806684A21E5B}"/>
   </bookViews>
@@ -561,6 +561,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -863,7 +867,34 @@
   <dimension ref="A1:AD78"/>
   <sheetFormatPr defaultColWidth="13.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="13.88671875" style="1"/>
+    <col min="1" max="1" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.88671875" style="1"/>
+    <col min="14" max="14" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="11.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="13.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="13.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="28.8" x14ac:dyDescent="0.3">
